--- a/bar-taste-plate/BAR_TASTE_PLATE_SPRING-SUMMER-2026.xlsx
+++ b/bar-taste-plate/BAR_TASTE_PLATE_SPRING-SUMMER-2026.xlsx
@@ -12,7 +12,7 @@
     <sheet name="SIDE 2 - BACK" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'SIDE 1 - FRONT'!$A$1:$K$35</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'SIDE 1 - FRONT'!$A$1:$K$34</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'SIDE 2 - BACK'!$A$1:$K$34</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="118">
   <si>
     <t xml:space="preserve">TOWNHALL   |   BAR TASTE PLATE   -   SPRING / SUMMER 2026</t>
   </si>
@@ -126,13 +126,13 @@
     <t xml:space="preserve">Lemons</t>
   </si>
   <si>
-    <t xml:space="preserve">Say Less</t>
+    <t xml:space="preserve">Light My Fire 2.0 Biz</t>
   </si>
   <si>
     <t xml:space="preserve">GARNISH &amp; DRY GOODS</t>
   </si>
   <si>
-    <t xml:space="preserve">Light My Fire 2.0 Biz</t>
+    <t xml:space="preserve">Turmeric Juice (LMF 2.0) *</t>
   </si>
   <si>
     <t xml:space="preserve">Olives</t>
@@ -141,111 +141,108 @@
     <t xml:space="preserve">-</t>
   </si>
   <si>
-    <t xml:space="preserve">Turmeric Juice (LMF 2.0) *</t>
+    <t xml:space="preserve">No New Friends Biz</t>
   </si>
   <si>
     <t xml:space="preserve">Mint</t>
   </si>
   <si>
-    <t xml:space="preserve">No New Friends Biz</t>
+    <t xml:space="preserve">Channel Orange Biz</t>
   </si>
   <si>
     <t xml:space="preserve">Parsley</t>
   </si>
   <si>
-    <t xml:space="preserve">Hot Girl Simmer Biz</t>
+    <t xml:space="preserve">Pear Chai Biz</t>
   </si>
   <si>
     <t xml:space="preserve">Basil</t>
   </si>
   <si>
-    <t xml:space="preserve">Alter Ego Biz</t>
+    <t xml:space="preserve">Don't Worry About It Sweetheart Biz</t>
   </si>
   <si>
     <t xml:space="preserve">Tarragon</t>
   </si>
   <si>
-    <t xml:space="preserve">Coconut Blue Spirulina</t>
+    <t xml:space="preserve">Cider Mix Biz</t>
   </si>
   <si>
     <t xml:space="preserve">Dehydrated Strawberries</t>
   </si>
   <si>
-    <t xml:space="preserve">Not Your Average Spritz</t>
+    <t xml:space="preserve">Chai Hard Biz</t>
   </si>
   <si>
     <t xml:space="preserve">Dried Calendula Flowers</t>
   </si>
   <si>
-    <t xml:space="preserve">Strawberry Allulose</t>
+    <t xml:space="preserve">Pecan Brown Simple</t>
   </si>
   <si>
     <t xml:space="preserve">Thai Chili</t>
   </si>
   <si>
-    <t xml:space="preserve">Tart Cherry Allulose</t>
+    <t xml:space="preserve">Scarlett Spritz Biz</t>
   </si>
   <si>
     <t xml:space="preserve">Hibiscus Leaves</t>
   </si>
   <si>
-    <t xml:space="preserve">Nitro Espresso Martini</t>
+    <t xml:space="preserve">JUICES &amp; MIXERS</t>
   </si>
   <si>
     <t xml:space="preserve">Cherries</t>
   </si>
   <si>
-    <t xml:space="preserve">JUICES &amp; MIXERS</t>
+    <t xml:space="preserve">Pineapple Juice</t>
   </si>
   <si>
     <t xml:space="preserve">Espresso Beans</t>
   </si>
   <si>
-    <t xml:space="preserve">Pineapple Juice</t>
+    <t xml:space="preserve">Orange Juice</t>
   </si>
   <si>
     <t xml:space="preserve">Dried Dragonfruit</t>
   </si>
   <si>
-    <t xml:space="preserve">Orange Juice</t>
+    <t xml:space="preserve">Grapefruit Juice</t>
   </si>
   <si>
     <t xml:space="preserve">Dragon Fruit Powder</t>
   </si>
   <si>
-    <t xml:space="preserve">Grapefruit Juice</t>
+    <t xml:space="preserve">Watermelon Juice</t>
   </si>
   <si>
     <t xml:space="preserve">Electrolyte Salt</t>
   </si>
   <si>
-    <t xml:space="preserve">Watermelon Juice</t>
+    <t xml:space="preserve">House Grenadine</t>
   </si>
   <si>
     <t xml:space="preserve">Jalapenos</t>
   </si>
   <si>
-    <t xml:space="preserve">House Grenadine</t>
+    <t xml:space="preserve">Olive Juice</t>
   </si>
   <si>
     <t xml:space="preserve">Salt</t>
   </si>
   <si>
-    <t xml:space="preserve">Olive Juice</t>
+    <t xml:space="preserve">Simple Syrup</t>
   </si>
   <si>
     <t xml:space="preserve">Sugar</t>
   </si>
   <si>
-    <t xml:space="preserve">Simple Syrup</t>
+    <t xml:space="preserve">Lemon Juice</t>
   </si>
   <si>
     <t xml:space="preserve">Angostura Bitters</t>
   </si>
   <si>
-    <t xml:space="preserve">Lemon Juice</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lime Juice</t>
   </si>
   <si>
@@ -258,7 +255,7 @@
     <t xml:space="preserve">* Turmeric Juice is for Light My Fire 2.0 - NOT the wellness shot.</t>
   </si>
   <si>
-    <t xml:space="preserve">Anything LOW or 86 -&gt; tell prep + a manager.</t>
+    <t xml:space="preserve">Blank PAR = new item, set its par.   LOW or 86 -&gt; tell prep + a manager.</t>
   </si>
   <si>
     <t xml:space="preserve">TURN OVER  -&gt;  SIDE 2:  BAR TOOLS, SET-UP &amp; DAILY COMMUNICATION</t>
@@ -433,12 +430,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0&quot; BTL&quot;"/>
     <numFmt numFmtId="166" formatCode="0&quot; PAN&quot;"/>
-    <numFmt numFmtId="167" formatCode="0&quot; CMB&quot;"/>
-    <numFmt numFmtId="168" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -713,7 +709,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -747,7 +743,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -774,7 +770,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -806,12 +802,16 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1110,7 +1110,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.5"/>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="C9" s="10"/>
       <c r="D9" s="11" t="str">
-        <f aca="false">IF(C9="","",MAX(0,B9-C9))</f>
+        <f aca="false">IF(OR(B9="",C9=""),"",MAX(0,B9-C9))</f>
         <v/>
       </c>
       <c r="E9" s="12"/>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="11" t="str">
-        <f aca="false">IF(I9="","",MAX(0,H9-I9))</f>
+        <f aca="false">IF(OR(H9="",I9=""),"",MAX(0,H9-I9))</f>
         <v/>
       </c>
       <c r="K9" s="12"/>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="11" t="str">
-        <f aca="false">IF(C10="","",MAX(0,B10-C10))</f>
+        <f aca="false">IF(OR(B10="",C10=""),"",MAX(0,B10-C10))</f>
         <v/>
       </c>
       <c r="E10" s="12"/>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="I10" s="10"/>
       <c r="J10" s="11" t="str">
-        <f aca="false">IF(I10="","",MAX(0,H10-I10))</f>
+        <f aca="false">IF(OR(H10="",I10=""),"",MAX(0,H10-I10))</f>
         <v/>
       </c>
       <c r="K10" s="12"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="11" t="str">
-        <f aca="false">IF(C11="","",MAX(0,B11-C11))</f>
+        <f aca="false">IF(OR(B11="",C11=""),"",MAX(0,B11-C11))</f>
         <v/>
       </c>
       <c r="E11" s="12"/>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="11" t="str">
-        <f aca="false">IF(C12="","",MAX(0,B12-C12))</f>
+        <f aca="false">IF(OR(B12="",C12=""),"",MAX(0,B12-C12))</f>
         <v/>
       </c>
       <c r="E12" s="12"/>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="11" t="str">
-        <f aca="false">IF(C13="","",MAX(0,B13-C13))</f>
+        <f aca="false">IF(OR(B13="",C13=""),"",MAX(0,B13-C13))</f>
         <v/>
       </c>
       <c r="E13" s="12"/>
@@ -1373,12 +1373,10 @@
       <c r="A14" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="B14" s="15"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11" t="str">
-        <f aca="false">IF(C14="","",MAX(0,B14-C14))</f>
+        <f aca="false">IF(OR(B14="",C14=""),"",MAX(0,B14-C14))</f>
         <v/>
       </c>
       <c r="E14" s="12"/>
@@ -1396,12 +1394,10 @@
       <c r="A15" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="B15" s="15"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11" t="str">
-        <f aca="false">IF(C15="","",MAX(0,B15-C15))</f>
+        <f aca="false">IF(OR(B15="",C15=""),"",MAX(0,B15-C15))</f>
         <v/>
       </c>
       <c r="E15" s="12"/>
@@ -1419,12 +1415,10 @@
       <c r="A16" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="B16" s="15"/>
       <c r="C16" s="10"/>
       <c r="D16" s="11" t="str">
-        <f aca="false">IF(C16="","",MAX(0,B16-C16))</f>
+        <f aca="false">IF(OR(B16="",C16=""),"",MAX(0,B16-C16))</f>
         <v/>
       </c>
       <c r="E16" s="12"/>
@@ -1442,12 +1436,10 @@
       <c r="A17" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="B17" s="15"/>
       <c r="C17" s="10"/>
       <c r="D17" s="11" t="str">
-        <f aca="false">IF(C17="","",MAX(0,B17-C17))</f>
+        <f aca="false">IF(OR(B17="",C17=""),"",MAX(0,B17-C17))</f>
         <v/>
       </c>
       <c r="E17" s="12"/>
@@ -1465,12 +1457,10 @@
       <c r="A18" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="B18" s="15"/>
       <c r="C18" s="10"/>
       <c r="D18" s="11" t="str">
-        <f aca="false">IF(C18="","",MAX(0,B18-C18))</f>
+        <f aca="false">IF(OR(B18="",C18=""),"",MAX(0,B18-C18))</f>
         <v/>
       </c>
       <c r="E18" s="12"/>
@@ -1488,12 +1478,10 @@
       <c r="A19" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="B19" s="15"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11" t="str">
-        <f aca="false">IF(C19="","",MAX(0,B19-C19))</f>
+        <f aca="false">IF(OR(B19="",C19=""),"",MAX(0,B19-C19))</f>
         <v/>
       </c>
       <c r="E19" s="12"/>
@@ -1511,12 +1499,10 @@
       <c r="A20" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="B20" s="15"/>
       <c r="C20" s="10"/>
       <c r="D20" s="11" t="str">
-        <f aca="false">IF(C20="","",MAX(0,B20-C20))</f>
+        <f aca="false">IF(OR(B20="",C20=""),"",MAX(0,B20-C20))</f>
         <v/>
       </c>
       <c r="E20" s="12"/>
@@ -1531,18 +1517,13 @@
       <c r="K20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="11" t="str">
-        <f aca="false">IF(C21="","",MAX(0,B21-C21))</f>
-        <v/>
-      </c>
-      <c r="E21" s="12"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
       <c r="G21" s="8" t="s">
         <v>40</v>
       </c>
@@ -1554,13 +1535,18 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
+      <c r="B22" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="11" t="str">
+        <f aca="false">IF(OR(B22="",C22=""),"",MAX(0,B22-C22))</f>
+        <v/>
+      </c>
+      <c r="E22" s="12"/>
       <c r="G22" s="8" t="s">
         <v>42</v>
       </c>
@@ -1580,7 +1566,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="11" t="str">
-        <f aca="false">IF(C23="","",MAX(0,B23-C23))</f>
+        <f aca="false">IF(OR(B23="",C23=""),"",MAX(0,B23-C23))</f>
         <v/>
       </c>
       <c r="E23" s="12"/>
@@ -1603,7 +1589,7 @@
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="11" t="str">
-        <f aca="false">IF(C24="","",MAX(0,B24-C24))</f>
+        <f aca="false">IF(OR(B24="",C24=""),"",MAX(0,B24-C24))</f>
         <v/>
       </c>
       <c r="E24" s="12"/>
@@ -1622,11 +1608,11 @@
         <v>47</v>
       </c>
       <c r="B25" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="11" t="str">
-        <f aca="false">IF(C25="","",MAX(0,B25-C25))</f>
+        <f aca="false">IF(OR(B25="",C25=""),"",MAX(0,B25-C25))</f>
         <v/>
       </c>
       <c r="E25" s="12"/>
@@ -1645,11 +1631,11 @@
         <v>49</v>
       </c>
       <c r="B26" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="11" t="str">
-        <f aca="false">IF(C26="","",MAX(0,B26-C26))</f>
+        <f aca="false">IF(OR(B26="",C26=""),"",MAX(0,B26-C26))</f>
         <v/>
       </c>
       <c r="E26" s="12"/>
@@ -1668,11 +1654,11 @@
         <v>51</v>
       </c>
       <c r="B27" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="11" t="str">
-        <f aca="false">IF(C27="","",MAX(0,B27-C27))</f>
+        <f aca="false">IF(OR(B27="",C27=""),"",MAX(0,B27-C27))</f>
         <v/>
       </c>
       <c r="E27" s="12"/>
@@ -1691,11 +1677,11 @@
         <v>53</v>
       </c>
       <c r="B28" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="11" t="str">
-        <f aca="false">IF(C28="","",MAX(0,B28-C28))</f>
+        <f aca="false">IF(OR(B28="",C28=""),"",MAX(0,B28-C28))</f>
         <v/>
       </c>
       <c r="E28" s="12"/>
@@ -1718,7 +1704,7 @@
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="11" t="str">
-        <f aca="false">IF(C29="","",MAX(0,B29-C29))</f>
+        <f aca="false">IF(OR(B29="",C29=""),"",MAX(0,B29-C29))</f>
         <v/>
       </c>
       <c r="E29" s="12"/>
@@ -1741,7 +1727,7 @@
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="11" t="str">
-        <f aca="false">IF(C30="","",MAX(0,B30-C30))</f>
+        <f aca="false">IF(OR(B30="",C30=""),"",MAX(0,B30-C30))</f>
         <v/>
       </c>
       <c r="E30" s="12"/>
@@ -1755,7 +1741,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="11" t="str">
-        <f aca="false">IF(C31="","",MAX(0,B31-C31))</f>
+        <f aca="false">IF(OR(B31="",C31=""),"",MAX(0,B31-C31))</f>
         <v/>
       </c>
       <c r="E31" s="12"/>
@@ -1765,59 +1751,45 @@
         <v>59</v>
       </c>
       <c r="B32" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C32" s="10"/>
       <c r="D32" s="11" t="str">
-        <f aca="false">IF(C32="","",MAX(0,B32-C32))</f>
+        <f aca="false">IF(OR(B32="",C32=""),"",MAX(0,B32-C32))</f>
         <v/>
       </c>
       <c r="E32" s="12"/>
     </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="11" t="str">
-        <f aca="false">IF(C33="","",MAX(0,B33-C33))</f>
-        <v/>
-      </c>
-      <c r="E33" s="12"/>
-    </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="G33" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="G34" s="16" t="s">
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+    </row>
+    <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-    </row>
-    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -1840,8 +1812,8 @@
     <mergeCell ref="H18:J18"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A22:E22"/>
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="H23:J23"/>
     <mergeCell ref="H24:J24"/>
@@ -1850,11 +1822,11 @@
     <mergeCell ref="H27:J27"/>
     <mergeCell ref="H28:J28"/>
     <mergeCell ref="H29:J29"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="G34:K34"/>
-    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="A34:K34"/>
   </mergeCells>
-  <conditionalFormatting sqref="D9:D33">
+  <conditionalFormatting sqref="D9:D32">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1864,7 +1836,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E9:E33">
+  <conditionalFormatting sqref="E9:E32">
     <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"86"</formula>
     </cfRule>
@@ -1875,7 +1847,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="Pick one from the drop-down." errorStyle="stop" errorTitle="Not on the list" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E9:E30 K9:K29 E31:E33" type="list">
+    <dataValidation allowBlank="true" error="Pick one from the drop-down." errorStyle="stop" errorTitle="Not on the list" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E9:E30 K9:K29 E31:E32" type="list">
       <formula1>"OK,LOW,86"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1925,7 +1897,7 @@
     </row>
     <row r="2" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1957,14 +1929,14 @@
     <row r="4" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="G5" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
@@ -1973,7 +1945,7 @@
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>8</v>
@@ -1985,10 +1957,10 @@
         <v>10</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="19" t="s">
         <v>68</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>69</v>
       </c>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
@@ -1997,7 +1969,7 @@
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="10"/>
@@ -2007,7 +1979,7 @@
       </c>
       <c r="E7" s="12"/>
       <c r="G7" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
@@ -2016,7 +1988,7 @@
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="10"/>
@@ -2026,7 +1998,7 @@
       </c>
       <c r="E8" s="12"/>
       <c r="G8" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
@@ -2035,7 +2007,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="10"/>
@@ -2047,7 +2019,7 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="10"/>
@@ -2057,7 +2029,7 @@
       </c>
       <c r="E10" s="12"/>
       <c r="G10" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
@@ -2066,7 +2038,7 @@
     </row>
     <row r="11" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="10"/>
@@ -2083,7 +2055,7 @@
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="10"/>
@@ -2100,7 +2072,7 @@
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="10"/>
@@ -2117,7 +2089,7 @@
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" s="22"/>
       <c r="C14" s="22"/>
@@ -2134,7 +2106,7 @@
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -2148,7 +2120,7 @@
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -2165,12 +2137,12 @@
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G17" s="21"/>
       <c r="H17" s="21"/>
@@ -2179,14 +2151,14 @@
       <c r="K17" s="21"/>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
       <c r="E18" s="10"/>
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
@@ -2195,14 +2167,14 @@
       <c r="K18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="B19" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
       <c r="E19" s="10"/>
       <c r="G19" s="21"/>
       <c r="H19" s="21"/>
@@ -2211,14 +2183,14 @@
       <c r="K19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
       <c r="E20" s="10"/>
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
@@ -2227,14 +2199,14 @@
       <c r="K20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
       <c r="E21" s="10"/>
       <c r="G21" s="21"/>
       <c r="H21" s="21"/>
@@ -2243,28 +2215,28 @@
       <c r="K21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="10"/>
-    </row>
-    <row r="23" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
+      <c r="B23" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="B23" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
       <c r="E23" s="10"/>
       <c r="G23" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
@@ -2272,139 +2244,139 @@
       <c r="K23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="10"/>
+      <c r="G24" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="10"/>
-      <c r="G24" s="26" t="s">
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+    </row>
+    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-    </row>
-    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
+      <c r="B25" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="10"/>
+      <c r="G25" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="10"/>
-      <c r="G25" s="26" t="s">
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+    </row>
+    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-    </row>
-    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
+      <c r="B26" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="10"/>
+      <c r="G26" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="10"/>
-      <c r="G26" s="26" t="s">
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-    </row>
-    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
+      <c r="B27" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="10"/>
-    </row>
-    <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
+      <c r="B28" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="10"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
+      <c r="B29" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="10"/>
+    </row>
+    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="10"/>
-    </row>
-    <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
+      <c r="B30" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="10"/>
+    </row>
+    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="10"/>
-    </row>
-    <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
+      <c r="B31" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="10"/>
+    </row>
+    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
+      <c r="B32" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="10"/>
+    </row>
+    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="B32" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="10"/>
-    </row>
-    <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B33" s="25" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
+      <c r="B33" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
       <c r="E33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
